--- a/daily_matches/job_matches_2026-09-01.xlsx
+++ b/daily_matches/job_matches_2026-09-01.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G64"/>
+  <dimension ref="A1:G43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AI Engineer Intern</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Copart, Inc</t>
+          <t>Vynca</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>26.7</v>
+        <v>20</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Hugging Face, Pinecone, Prompt Engineering, TensorFlow, PyTorch</t>
+          <t>RAG, Redshift, BigQuery, Data Lake, Kinesis, FastAPI, Kubernetes, CI/CD, Snowflake, BigQuery</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=222ed3cc9231d113</t>
+          <t>https://www.indeed.com/viewjob?jk=1d41697c1443e407</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Royal Caribbean Group</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Miramar, FL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>24.4</v>
+        <v>18.9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, Copilot, Redshift, BigQuery, Data Lake, Kinesis, CI/CD, Git</t>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Hugging Face, FAISS, Pinecone, Prompt Engineering, XGBoost, spaCy</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,67 +531,67 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15bc705887f3d3f9</t>
+          <t>https://www.indeed.com/viewjob?jk=e874dace146eebbf</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Service Delivery Center, AI &amp; Data, AI Developer - Senior</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>Consumer Cellular</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>20</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, LLaMA, Copilot, Pinecone, Prompt Engineering, AWS SageMaker, Azure ML, Docker</t>
+          <t>AI Engineer, Generative AI, RAG, LLaMA, Gemini, Prompt Engineering, TensorFlow, PyTorch, Git, Python</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=596853b0b1c16180</t>
+          <t>https://www.indeed.com/viewjob?jk=ddfafc898b018bfa</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Engineering – Senior Engineer</t>
+          <t>Data and AI Engineer II</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>FICO</t>
+          <t>Freeport-McMoRan</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.9</v>
+        <v>15.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, Kafka, PostgreSQL, MySQL, MongoDB</t>
+          <t>AI Engineer, Data Scientist, Generative AI, RAG, Cortex, Docker, CI/CD, GitHub Actions, Git, Snowflake</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ff95b66842bb690</t>
+          <t>https://www.indeed.com/viewjob?jk=f3bb3edbb44ae52d</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sr AI/Agentic Engineer</t>
+          <t>Site Reliability Engineer I</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Lendistry</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Sunrise, FL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>15.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, Gemini, Copilot, Hugging Face, Pinecone, Prompt Engineering, Docker</t>
+          <t>Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, PostgreSQL, MySQL, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa4ba27f42424693</t>
+          <t>https://www.indeed.com/viewjob?jk=af69fed96c27a33f</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sr AI/Agentic Engineer</t>
+          <t>Specialist IS Business Systems Analyst</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Lendistry</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Thousand Oaks, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>15.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, Gemini, Copilot, Hugging Face, Pinecone, Prompt Engineering, Docker</t>
+          <t>RAG, S3, EC2, Redshift, AKS, CI/CD, Git, Databricks, Redshift, Tableau</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,67 +671,67 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64293f039ef69c4a</t>
+          <t>https://www.indeed.com/viewjob?jk=c6db11c42ce1f3de</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sr AI/Agentic Engineer</t>
+          <t>Artificial Intelligence (AI) Engineer (Senior)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Lendistry</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>13.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, Gemini, Copilot, Hugging Face, Pinecone, Prompt Engineering, Docker</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, LangChain, TensorFlow, PyTorch, Docker, CI/CD, Python</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05c772e2f06ba4b9</t>
+          <t>https://www.indeed.com/viewjob?jk=a6a1e3591640c001</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sr AI/Agentic Engineer</t>
+          <t>Senior Software Developer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Lendistry</t>
+          <t>Prodapt Solutions</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16.7</v>
+        <v>13.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, Gemini, Copilot, Hugging Face, Pinecone, Prompt Engineering, Docker</t>
+          <t>RAG, Copilot, Docker, Kubernetes, AKS, CI/CD, Jenkins, Git, R, Java</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5f9bf048a2e2be0</t>
+          <t>https://www.indeed.com/viewjob?jk=e49334a6de85ce3c</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sr AI/Agentic Engineer</t>
+          <t>Mid-Level DATA ENGINEER: Microsoft Power Platform &amp; AI Copilot Studio (HYBRID)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Lendistry</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Tustin, CA, US USA</t>
+          <t>Bloomington, IL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16.7</v>
+        <v>13.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, Gemini, Copilot, Hugging Face, Pinecone, Prompt Engineering, Docker</t>
+          <t>Generative AI, RAG, Copilot, Synapse, CI/CD, Snowflake, Databricks, Power BI, Python, SQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,67 +776,67 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72b16e59ef226de8</t>
+          <t>https://www.indeed.com/viewjob?jk=75d140e1ecf0b230</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AI Forward Deployed Engineer</t>
+          <t>Junior AI Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Fixez</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15.6</v>
+        <v>12.2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, Gemini, Copilot, Docker, Kubernetes, CI/CD, Git</t>
+          <t>AI Engineer, Data Scientist, Generative AI, RAG, TensorFlow, Hadoop, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05fca0179dc26718</t>
+          <t>https://www.indeed.com/viewjob?jk=c67ef0b9203f7341</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Senior Dev Ops Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Banc of California</t>
+          <t>Ecentria</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Northbrook, IL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, Synapse, Data Lake, CI/CD, Terraform, Git, Snowflake, Power BI, Python, SQL</t>
+          <t>RAG, Docker, Kubernetes, Terraform, Git, MySQL, Cassandra, Python, SQL, R</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29ffdd693ba7b433</t>
+          <t>https://www.indeed.com/viewjob?jk=5a8f7629eee2b42e</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ServiceTitan</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Redshift, Git, Snowflake, Redshift, Kafka, PostgreSQL, Python, SQL</t>
+          <t>Data Scientist, RAG, Redshift, Snowflake, Databricks, Redshift, Tableau, Power BI, Python, R</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00dce8c243c5b7df</t>
+          <t>https://www.indeed.com/viewjob?jk=06e89e071d888b20</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Web Developer Full Stack Engineer</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Data Lake, FastAPI, Docker, CI/CD, GitHub Actions, Git, Databricks, PostgreSQL</t>
+          <t>RAG, BigQuery, FastAPI, Kubernetes, BigQuery, Kafka, PostgreSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80dae622ba00b61b</t>
+          <t>https://www.indeed.com/viewjob?jk=0a1a2f9a9e5b8591</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Web Developer Full Stack Engineer</t>
+          <t>Senior Platform Engineer, Product Facing Systems (Remote)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>Abercrombie &amp; Fitch</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Data Lake, FastAPI, Docker, CI/CD, GitHub Actions, Git, Databricks, PostgreSQL</t>
+          <t>RAG, Kubernetes, AKS, CI/CD, Terraform, Git, Kafka, R, Java, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b767341125ef88f</t>
+          <t>https://www.indeed.com/viewjob?jk=4af6c33eca425d4d</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Generative AI Architect</t>
+          <t>Software Engineer, Full Stack</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>J2B GLOBAL LLC</t>
+          <t>CoBank</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Greenwood Village, CO, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Pinecone, Prompt Engineering, TensorFlow, PyTorch, Python</t>
+          <t>Generative AI, RAG, TensorFlow, Docker, Kubernetes, CI/CD, Git, Python, SQL, R</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6e01633249699fc</t>
+          <t>https://www.indeed.com/viewjob?jk=6f438d97a6b9c97a</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AI Automation Engineer</t>
+          <t>Distinguished Cloud Architect (R-19605)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Fairlife, LLC</t>
+          <t>Dun &amp; Bradstreet</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Florham Park, NJ, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Machine Learning Engineer, LangChain, RAG, Pinecone, ChromaDB, Prompt Engineering, Docker, Git</t>
+          <t>RAG, BigQuery, Docker, Kubernetes, CI/CD, Terraform, BigQuery, Python, SQL, R</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20c8b73b91db8a27</t>
+          <t>https://www.indeed.com/viewjob?jk=b9b428765718be76</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Software Engineer III-Python/PySpark</t>
+          <t>Drupal Developer – Senior</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>NuAxis Innovations</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, CI/CD, Git, Snowflake, Databricks, PySpark, Python, SQL, R</t>
+          <t>S3, Docker, Kubernetes, CI/CD, Git, Kafka, MySQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcb46275b507c630</t>
+          <t>https://www.indeed.com/viewjob?jk=de484ff1a65cd9c4</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>OCI Cloud Engineer</t>
+          <t>AI Software Engineer (MTS) – Digital Success Engineering</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, MySQL, Python, SQL</t>
+          <t>Generative AI, RAG, Prompt Engineering, CI/CD, Git, Python, R, Java, Optimization, A/B Testing</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=168bc86279b2f3a1</t>
+          <t>https://www.indeed.com/viewjob?jk=745b163f3582d495</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>OCI Solutions Architect</t>
+          <t>AI &amp; Data Architect, US</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, MySQL, Python, SQL</t>
+          <t>Generative AI, RAG, Data Lake, Kubernetes, Python, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=133fdba617ad39ad</t>
+          <t>https://www.indeed.com/viewjob?jk=89e252d5bd93de93</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Cloud-Native Architect</t>
+          <t>AI &amp; Data Architect, US</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Kafka, Python, R, Java</t>
+          <t>Generative AI, RAG, Data Lake, Kubernetes, Python, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bba1497145f4051</t>
+          <t>https://www.indeed.com/viewjob?jk=93d7d5736a76526c</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Autonomous Learning Engineer</t>
+          <t>Software Engineer - CHG (Hybrid)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Python, R</t>
+          <t>RAG, Kubernetes, Terraform, Git, Kafka, PostgreSQL, NoSQL, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b494456e083d031e</t>
+          <t>https://www.indeed.com/viewjob?jk=e1c855c396d5779f</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Full-Stack Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Grainger</t>
+          <t>onXmaps</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, GitHub Actions, Git, Snowflake, Databricks, PySpark, Python, SQL, R</t>
+          <t>Docker, Kubernetes, Terraform, Git, PostgreSQL, MySQL, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6ac749b1ab9e374</t>
+          <t>https://www.indeed.com/viewjob?jk=c727b26bae684ab1</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Personalization Product Senior Data Associate</t>
+          <t>Sr Cloud Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Marriott Vacations Worldwide</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, Data Lake, Git, Snowflake, Tableau, Python, SQL, R</t>
+          <t>RAG, Copilot, Kubernetes, Terraform, Git, Kafka, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a9cce5a85bd5639</t>
+          <t>https://www.indeed.com/viewjob?jk=53d0611fc1f1e6be</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Java Application Architect</t>
+          <t>Software Development Engineer in Test - AI</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Delos Data</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlottesville, VA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, Kafka, PostgreSQL, MySQL, SQL, R</t>
+          <t>Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eac8dc0954e3729c</t>
+          <t>https://www.indeed.com/viewjob?jk=12038b5df30a63c5</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Software Engineer - Sr. Consultant level</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Upper Hand</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, Jenkins, Git, Kafka, MySQL, NoSQL, SQL, R</t>
+          <t>RAG, BigQuery, CI/CD, Git, BigQuery, PostgreSQL, SQL, R, Java, Optimization</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8008449c42bd427</t>
+          <t>https://www.indeed.com/viewjob?jk=478485da80bebeae</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Software Development Engineer - US Federal</t>
+          <t>2027 Intern - Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Workday</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Java</t>
+          <t>Machine Learning Engineer, Generative AI, LangChain, RAG, Hugging Face, TensorFlow, PyTorch, Python, R, Java</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,102 +1371,102 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee75da69e5cdf2fa</t>
+          <t>https://www.indeed.com/viewjob?jk=839163cfbd39cb5e</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Generative AI Engineer</t>
+          <t>Remote ai contributor</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>INFINITE ELECTRONICS</t>
+          <t>West Tech</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Lewisville, TX, US USA</t>
+          <t>Clayton, NC, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, FastAPI, Docker, CI/CD, PySpark, Python, R, Scala</t>
+          <t>Generative AI, RAG, TensorFlow, PyTorch, Hadoop, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63e030388c42500b</t>
+          <t>https://www.indeed.com/viewjob?jk=4b6a60c698772f4c</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Generative AI Engineer</t>
+          <t>DATA SCIENTIST</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>INFINITE ELECTRONICS</t>
+          <t>Dollar General</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Goodlettsville, TN, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, FastAPI, Docker, CI/CD, PySpark, Python, R, Scala</t>
+          <t>Data Scientist, Git, Databricks, PySpark, Tableau, Matplotlib, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28236ac1d6aa91b3</t>
+          <t>https://www.indeed.com/viewjob?jk=93f3bbe6c6eb3335</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Generative AI Developer</t>
+          <t>Junior Software Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Marsh McLennan Agency</t>
+          <t>HouseMax Funding</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>White Plains, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Pinecone, Prompt Engineering, CI/CD, Git, Python, R, Scala</t>
+          <t>RAG, Copilot, Git, PostgreSQL, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a3aaf884236bb22</t>
+          <t>https://www.indeed.com/viewjob?jk=43db0fee933b6487</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Software Development Tester</t>
+          <t>AI Platform Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Prompt Engineering, CI/CD, GitHub Actions, Git, NoSQL, SQL, R, Java</t>
+          <t>Generative AI, MLflow, Kubernetes, CI/CD, Git, Python, R, Java, Optimization</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b097e917dd1a75c6</t>
+          <t>https://www.indeed.com/viewjob?jk=bd7f92ef422e6865</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Sr Software Engineer, AI Engineer</t>
+          <t>Digital Technology Organization Rotational Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Vivint</t>
+          <t>PENNYMAC</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Carrollton, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, TensorFlow, PyTorch, OpenCV, Git, NoSQL, Python, SQL, R</t>
+          <t>RAG, Gemini, Copilot, Prompt Engineering, Git, MySQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0a47ebec8f5f5a6</t>
+          <t>https://www.indeed.com/viewjob?jk=ece014134dbfb6ce</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Technology Development Program Associate - February 2027</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Super Micro Computer, Inc.</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Jenkins, Terraform, NoSQL, Python, SQL, R, Java</t>
+          <t>LangChain, RAG, Docker, Git, Hadoop, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef7c81c1f347080d</t>
+          <t>https://www.indeed.com/viewjob?jk=d5e68423d25b95a9</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Analyst, Data Analytics</t>
+          <t>Senior Database Engineer - Remote</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>T. Rowe Price</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Copilot, Git, Snowflake, Tableau, Power BI, Python, SQL, R, Scala, Optimization</t>
+          <t>CI/CD, Git, PostgreSQL, MySQL, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aef8bfb5adf47071</t>
+          <t>https://www.indeed.com/viewjob?jk=341b8b7d68e7994b</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Associate Data Scientist/ Data Scientist</t>
+          <t>Senior Software Engineer, Data Engineering</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Navy Federal Credit Union</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, Copilot, XGBoost, AKS, Git, Databricks, Python, SQL, R</t>
+          <t>RAG, Kubernetes, Terraform, Git, Kafka, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f3cfbeb6a0d5322</t>
+          <t>https://www.indeed.com/viewjob?jk=6b1070c522d395ed</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>AI Platform Engineer</t>
+          <t>Cyber Threat Defense Sr AI/ML Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>United States Cold Storage</t>
+          <t>Bank of America</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Copilot, Prompt Engineering, CI/CD, Git, Python, SQL, R</t>
+          <t>Machine Learning Engineer, Generative AI, LangChain, RAG, Hugging Face, PyTorch, Python, R, Scala</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d94c5f6949e0fce</t>
+          <t>https://www.indeed.com/viewjob?jk=a5aecf5dad5b36ed</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer III</t>
+          <t>Senior Agentic AI Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Evergen</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Scala</t>
+          <t>AI Engineer, LangChain, RAG, Copilot, Git, Snowflake, Python, R, Scala</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d112005b7fa18a95</t>
+          <t>https://www.indeed.com/viewjob?jk=5e547dd05c4bd930</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>AI Platform Engineer</t>
+          <t>Senior Developer – Full Stack</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>NuAxis Innovations</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala, Optimization</t>
+          <t>RAG, Copilot, Kubernetes, CI/CD, Kafka, MySQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75649a2a273f051e</t>
+          <t>https://www.indeed.com/viewjob?jk=9606ad9dcbf80460</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Full-Stack Engineer</t>
+          <t>IT Web Developer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>OnX</t>
+          <t>NuAxis Innovations</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, Terraform, Git, PostgreSQL, MySQL, Python, SQL, R, Scala</t>
+          <t>Copilot, S3, CI/CD, Git, Kafka, PostgreSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55bd3b56f8c9510d</t>
+          <t>https://www.indeed.com/viewjob?jk=4300e851986e6585</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Engineer, ML Data Services</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Motional</t>
+          <t>HDR</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Sioux Falls, SD, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Copilot, S3, Redshift, Docker, Git, Redshift, Python, R, Java, Scala</t>
+          <t>Data Scientist, RAG, Tableau, Power BI, Matplotlib, Seaborn, Python, SQL, R</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10208da6da41d304</t>
+          <t>https://www.indeed.com/viewjob?jk=a639c248a691afa1</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Engineer, ML Data Services</t>
+          <t>Economist, Ramp Economics Lab</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Motional</t>
+          <t>Ramp</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Copilot, S3, Redshift, Docker, Git, Redshift, Python, R, Java, Scala</t>
+          <t>Data Scientist, RAG, Redshift, BigQuery, Snowflake, BigQuery, Redshift, SQL, R</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=473eb45015763f16</t>
+          <t>https://www.indeed.com/viewjob?jk=c533c1cf2527666a</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Software Architecture - Sr Advisor I</t>
+          <t>Economist, Ramp Economics Lab</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Ramp</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Git, Kafka, PostgreSQL, SQL, R, Scala, Optimization</t>
+          <t>Data Scientist, RAG, Redshift, BigQuery, Snowflake, BigQuery, Redshift, SQL, R</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90013a4dc205f0f8</t>
+          <t>https://www.indeed.com/viewjob?jk=e749d6169f5f9a7c</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Machine Learning Engineering (ML Apps)</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>Instacart</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Generative AI, PyTorch, Docker, CI/CD, Git, Python, R, Java, Optimization</t>
+          <t>RAG, Copilot, Snowflake, Tableau, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,742 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b20a99fbf24108e</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Software Development Engineer in Test - AI</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Delos Data</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D44" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cc827aad1b4b9d1a</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Cloud Infrastructure and Security Engineer</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Harris Associates</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D45" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>RAG, Kubernetes, AKS, CI/CD, Terraform, Snowflake, Databricks, Power BI, R, Scala</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=41caf945fea11cfd</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>MLOps Research Engineer</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Merge Labs</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D46" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, PyTorch, MLflow, Kubernetes, CI/CD, Git, Python, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b5ceb4b555afba81</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>AI-Centric Release &amp; Automation Software Engineer</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>General Motors (GM)</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Sunnyvale, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D47" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, Jenkins, GitHub Actions, Git, Power BI, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f342fde2939be0a1</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Energy Data Scientist</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>EnergyHub</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Burlington, VT, US USA</t>
-        </is>
-      </c>
-      <c r="D48" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>Data Scientist, TensorFlow, Snowflake, Databricks, Tableau, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ea4dcf33b2c6a0fa</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Energy Data Scientist</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>EnergyHub</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D49" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>Data Scientist, TensorFlow, Snowflake, Databricks, Tableau, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=41548be738a76cc8</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Energy Data Scientist</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>EnergyHub</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D50" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>Data Scientist, TensorFlow, Snowflake, Databricks, Tableau, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8103a63d2d3d1da7</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Energy Data Scientist</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>EnergyHub</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Denver, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D51" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>Data Scientist, TensorFlow, Snowflake, Databricks, Tableau, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=13f4312108b4db79</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Energy Data Scientist</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>EnergyHub</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D52" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>Data Scientist, TensorFlow, Snowflake, Databricks, Tableau, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=26603fc5c3af6f4d</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Conversational AI/ Chatbot Developer</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Diverse Agile Solutions</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Adelphi, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D53" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Copilot, CI/CD, GitHub Actions, Git, Power BI, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8a81c994d5c135c3</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - Integrations - AI/ML</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>clickhouse</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D54" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>Data Scientist, LangChain, RAG, LLaMA, Kafka, Tableau, Python, SQL, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1251b27601bc9eff</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Software Engineer III (Java/AWS)</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D55" t="n">
-        <v>10</v>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>RAG, S3, EC2, CI/CD, Git, Cassandra, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5aaa31990e0d8669</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Senior AI Architect</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>SIA</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D56" t="n">
-        <v>10</v>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Terraform, Git, Databricks, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f8652dc74907d4f2</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>Senior SDET — Mobile Automation Engineer</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Fanatics</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D57" t="n">
-        <v>10</v>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, Prompt Engineering, CI/CD, GitHub Actions, Git, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ed1ea5d52a8db652</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>Advanced Data Scientist</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Honeywell</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Township of Hamilton, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D58" t="n">
-        <v>10</v>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, Git, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2b31484d8b65106f</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>AI First Engineer – Oracle SCM Applications Suite</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Cognizant</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D59" t="n">
-        <v>10</v>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Copilot, Prompt Engineering, Git, SQL, R, Java, Optimization</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7e752286322e650a</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>Senior Engineer</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>Nexus One</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D60" t="n">
-        <v>10</v>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>Data Lake, Kinesis, Terraform, Kafka, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=73fcaa363d33fefe</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>Economist, Ramp Economics Lab</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Ramp</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D61" t="n">
-        <v>10</v>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Redshift, BigQuery, Snowflake, BigQuery, Redshift, SQL, R</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cb1740f61d0f83c8</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>NIKE, Inc. Artificial Intelligence, Data, &amp; Machine Learning Engineering Undergraduate Internship</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>NIKE</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Beaverton, OR, US USA</t>
-        </is>
-      </c>
-      <c r="D62" t="n">
-        <v>10</v>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer, Generative AI, RAG, CI/CD, Databricks, Tableau, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5fa7e8044f8008fc</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>Data Scientist II</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>Lennox International</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Richardson, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D63" t="n">
-        <v>10</v>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>Data Scientist, TensorFlow, PySpark, Tableau, Power BI, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cff70e26f1d4eb29</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>Overseas Contractor</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>LTM Limited</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D64" t="n">
-        <v>10</v>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>LangChain, RAG, Pinecone, Prompt Engineering, Kubernetes, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4c345b1ca49e8bf8</t>
+          <t>https://www.indeed.com/viewjob?jk=111187c8fe573b22</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-09-01.xlsx
+++ b/daily_matches/job_matches_2026-09-01.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G43"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Vynca</t>
+          <t>Aramark</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20</v>
+        <v>22.2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, Redshift, BigQuery, Data Lake, Kinesis, FastAPI, Kubernetes, CI/CD, Snowflake, BigQuery</t>
+          <t>Copilot, S3, EC2, BigQuery, FastAPI, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d41697c1443e407</t>
+          <t>https://www.indeed.com/viewjob?jk=39460deda6cc7046</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Machine Learning Engineer II, Document &amp; Vision Intelligence</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.9</v>
+        <v>22.2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, Hugging Face, FAISS, Pinecone, Prompt Engineering, XGBoost, spaCy</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, RAG, TensorFlow, PyTorch, Keras, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e874dace146eebbf</t>
+          <t>https://www.indeed.com/viewjob?jk=43f2ff091a75531a</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Machine Learning Engineer II, Document &amp; Vision Intelligence</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Consumer Cellular</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16.7</v>
+        <v>22.2</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, LLaMA, Gemini, Prompt Engineering, TensorFlow, PyTorch, Git, Python</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, RAG, TensorFlow, PyTorch, Keras, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddfafc898b018bfa</t>
+          <t>https://www.indeed.com/viewjob?jk=1dde48c17b527b0d</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data and AI Engineer II</t>
+          <t>Machine Learning Engineer II, Document &amp; Vision Intelligence</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Freeport-McMoRan</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15.6</v>
+        <v>22.2</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, Cortex, Docker, CI/CD, GitHub Actions, Git, Snowflake</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, RAG, TensorFlow, PyTorch, Keras, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,59 +601,59 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3bb3edbb44ae52d</t>
+          <t>https://www.indeed.com/viewjob?jk=341131fbbffbdd46</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer I</t>
+          <t>Data Solutions Architect</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Smart Tech Skills LLC</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15.6</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, PostgreSQL, MySQL, Cassandra, NoSQL</t>
+          <t>S3, Glue, Synapse, CI/CD, Terraform, Git, Snowflake, Databricks, PySpark, Kafka</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af69fed96c27a33f</t>
+          <t>https://www.indeed.com/viewjob?jk=501460a7402af538</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Specialist IS Business Systems Analyst</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Pacific Gas and Electric</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Thousand Oaks, CA, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,42 +661,42 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Redshift, AKS, CI/CD, Git, Databricks, Redshift, Tableau</t>
+          <t>RAG, S3, EC2, Redshift, Synapse, Data Lake, CI/CD, Terraform, Redshift, NoSQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6db11c42ce1f3de</t>
+          <t>https://www.indeed.com/viewjob?jk=2c7c0ea011bc1581</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Artificial Intelligence (AI) Engineer (Senior)</t>
+          <t>Campus Graduate Masters Summer Internship Program - 2027 Data Engineer, Enterprise Technology Services- Charlotte, NC</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, LangChain, TensorFlow, PyTorch, Docker, CI/CD, Python</t>
+          <t>RAG, BigQuery, CI/CD, Git, BigQuery, PostgreSQL, MongoDB, Cassandra, NoSQL, Python</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,102 +706,102 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6a1e3591640c001</t>
+          <t>https://www.indeed.com/viewjob?jk=615c775c5cae3f87</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Software Developer</t>
+          <t>Campus Graduate Masters Summer Internship Program - 2027 Data Engineer, Enterprise Technology Services- Phoenix, AZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Prodapt Solutions</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, AKS, CI/CD, Jenkins, Git, R, Java</t>
+          <t>RAG, BigQuery, CI/CD, Git, BigQuery, PostgreSQL, MongoDB, Cassandra, NoSQL, Python</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e49334a6de85ce3c</t>
+          <t>https://www.indeed.com/viewjob?jk=e7c88978b19e1fac</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Mid-Level DATA ENGINEER: Microsoft Power Platform &amp; AI Copilot Studio (HYBRID)</t>
+          <t>Campus Graduate Masters Summer Internship Program - 2027 Data Engineer, Enterprise Technology Services- Sunrise, FL</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bloomington, IL, US USA</t>
+          <t>Sunrise, FL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, Synapse, CI/CD, Snowflake, Databricks, Power BI, Python, SQL</t>
+          <t>RAG, BigQuery, CI/CD, Git, BigQuery, PostgreSQL, MongoDB, Cassandra, NoSQL, Python</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75d140e1ecf0b230</t>
+          <t>https://www.indeed.com/viewjob?jk=24d421e34cea4cb0</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Junior AI Engineer</t>
+          <t>Business Analyst</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Fixez</t>
+          <t>Ness Digital Engineering</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, TensorFlow, Hadoop, Python, SQL, R, Java</t>
+          <t>Redshift, BigQuery, Kinesis, Git, Snowflake, Databricks, BigQuery, Redshift, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,67 +811,67 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c67ef0b9203f7341</t>
+          <t>https://www.indeed.com/viewjob?jk=ef3f1d7e3dce5d5b</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Dev Ops Engineer</t>
+          <t>Business Analyst</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Ecentria</t>
+          <t>Ness Digital Engineering</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Northbrook, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Terraform, Git, MySQL, Cassandra, Python, SQL, R</t>
+          <t>Redshift, BigQuery, Kinesis, Git, Snowflake, Databricks, BigQuery, Redshift, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a8f7629eee2b42e</t>
+          <t>https://www.indeed.com/viewjob?jk=26924b3ed57d2d37</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior AI Engineer (Ph.D. required)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Exponent</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Redshift, Snowflake, Databricks, Redshift, Tableau, Power BI, Python, R</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Copilot, Pinecone, Prompt Engineering, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,137 +881,137 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06e89e071d888b20</t>
+          <t>https://www.indeed.com/viewjob?jk=89ff4cd5ab679967</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Campus Undergraduate Summer Internship Program - 2027 Data Engineer, Enterprise Technology Services- Phoenix, AZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, FastAPI, Kubernetes, BigQuery, Kafka, PostgreSQL, Python, SQL, R</t>
+          <t>RAG, BigQuery, Git, BigQuery, PostgreSQL, MongoDB, Cassandra, Python, SQL, R</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a1a2f9a9e5b8591</t>
+          <t>https://www.indeed.com/viewjob?jk=21c4624adc67b18e</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer, Product Facing Systems (Remote)</t>
+          <t>Campus Undergraduate Summer Internship Program - 2027 Data Engineer, Enterprise Technology Services- Charlotte, NC</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Abercrombie &amp; Fitch</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, AKS, CI/CD, Terraform, Git, Kafka, R, Java, Scala</t>
+          <t>RAG, BigQuery, Git, BigQuery, PostgreSQL, MongoDB, Cassandra, Python, SQL, R</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4af6c33eca425d4d</t>
+          <t>https://www.indeed.com/viewjob?jk=4a1f26919bbd5f4b</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Software Engineer, Full Stack</t>
+          <t>Campus Undergraduate Summer Internship Program - 2027 Data Engineer, Enterprise Technology Services- Sunrise, FL</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CoBank</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Greenwood Village, CO, US USA</t>
+          <t>Sunrise, FL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, TensorFlow, Docker, Kubernetes, CI/CD, Git, Python, SQL, R</t>
+          <t>RAG, BigQuery, Git, BigQuery, PostgreSQL, MongoDB, Cassandra, Python, SQL, R</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f438d97a6b9c97a</t>
+          <t>https://www.indeed.com/viewjob?jk=5f6abea4f1a0a28b</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Distinguished Cloud Architect (R-19605)</t>
+          <t>Mid-Level DATA ENGINEER: Microsoft Power Platform &amp; AI Copilot Studio (HYBRID)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Dun &amp; Bradstreet</t>
+          <t>State Farm</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Florham Park, NJ, US USA</t>
+          <t>Bloomington, IL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Docker, Kubernetes, CI/CD, Terraform, BigQuery, Python, SQL, R</t>
+          <t>Generative AI, RAG, Copilot, Synapse, CI/CD, Snowflake, Databricks, Power BI, Python, SQL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9b428765718be76</t>
+          <t>https://www.indeed.com/viewjob?jk=d276a1bbc3a5d721</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Drupal Developer – Senior</t>
+          <t>Site Reliability Engineer- REMOTE - Onsite Training</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>NuAxis Innovations</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>S3, Docker, Kubernetes, CI/CD, Git, Kafka, MySQL, SQL, R, Java</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de484ff1a65cd9c4</t>
+          <t>https://www.indeed.com/viewjob?jk=fbb47baecd105cce</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AI Software Engineer (MTS) – Digital Success Engineering</t>
+          <t>Software Engineer II (React/Java)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Prompt Engineering, CI/CD, Git, Python, R, Java, Optimization, A/B Testing</t>
+          <t>RAG, Copilot, Kubernetes, CI/CD, Git, Kafka, Cassandra, NoSQL, SQL, R</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=745b163f3582d495</t>
+          <t>https://www.indeed.com/viewjob?jk=68a43b6923d695d9</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AI &amp; Data Architect, US</t>
+          <t>Sr Applied Data Scientist - Personalization (applied ML, PyTorch, RecSys)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Brooklyn Park, MN, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Data Lake, Kubernetes, Python, SQL, R, Java, Scala, Optimization</t>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, PyTorch, Git, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,59 +1126,59 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89e252d5bd93de93</t>
+          <t>https://www.indeed.com/viewjob?jk=8bd7f263656a978a</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AI &amp; Data Architect, US</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>CENSYS</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Data Lake, Kubernetes, Python, SQL, R, Java, Scala, Optimization</t>
+          <t>RAG, Copilot, S3, Synapse, Docker, Kubernetes, CI/CD, Kafka, Python, R</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93d7d5736a76526c</t>
+          <t>https://www.indeed.com/viewjob?jk=37c6fcd4a82da612</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Software Engineer - CHG (Hybrid)</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Propio LS LLC</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, Terraform, Git, Kafka, PostgreSQL, NoSQL, SQL, R, Scala</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Hugging Face, CI/CD, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1c855c396d5779f</t>
+          <t>https://www.indeed.com/viewjob?jk=9ca8aa6e56948dee</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Full-Stack Engineer</t>
+          <t>Senior Machine Learning Engineer, Accelerated Apache Spark</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>onXmaps</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, Terraform, Git, PostgreSQL, MySQL, Python, SQL, R, Scala</t>
+          <t>Machine Learning Engineer, TensorFlow, PyTorch, XGBoost, Python, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c727b26bae684ab1</t>
+          <t>https://www.indeed.com/viewjob?jk=38648a895bf31cd4</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Sr Cloud Engineer</t>
+          <t>Senior Software Engineer - WGU Labs</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Marriott Vacations Worldwide</t>
+          <t>Western Governors University</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Kubernetes, Terraform, Git, Kafka, Python, R, Scala, Optimization</t>
+          <t>RAG, FastAPI, Docker, Kubernetes, Terraform, PostgreSQL, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53d0611fc1f1e6be</t>
+          <t>https://www.indeed.com/viewjob?jk=46d267432b1efe9f</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test - AI</t>
+          <t>Senior Associate - Full-Stack AI Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Delos Data</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Charlottesville, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R, Scala</t>
+          <t>AI Engineer, Generative AI, RAG, Prompt Engineering, Kubernetes, CI/CD, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12038b5df30a63c5</t>
+          <t>https://www.indeed.com/viewjob?jk=54ae268af26a65ff</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Engineer, Facilities Automation</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Upper Hand</t>
+          <t>Micron Technology</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, CI/CD, Git, BigQuery, PostgreSQL, SQL, R, Java, Optimization</t>
+          <t>RAG, Copilot, Git, Snowflake, Power BI, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=478485da80bebeae</t>
+          <t>https://www.indeed.com/viewjob?jk=f2bf393f6b205724</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2027 Intern - Machine Learning Engineer</t>
+          <t>Sr. Data Analyst</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Reserv</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,42 +1361,42 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Generative AI, LangChain, RAG, Hugging Face, TensorFlow, PyTorch, Python, R, Java</t>
+          <t>RAG, BigQuery, Git, Snowflake, BigQuery, Tableau, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=839163cfbd39cb5e</t>
+          <t>https://www.indeed.com/viewjob?jk=92c3d91ad7bed240</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Remote ai contributor</t>
+          <t>Digital Experience IS Intern: Summer 2027</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>West Tech</t>
+          <t>Blue Cross Blue Shield of Nebraska</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Clayton, NC, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, TensorFlow, PyTorch, Hadoop, Python, SQL, R, Java, Scala</t>
+          <t>RAG, Copilot, Prompt Engineering, AKS, Git, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,59 +1406,59 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b6a60c698772f4c</t>
+          <t>https://www.indeed.com/viewjob?jk=9cbdb34dd3cfbe01</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>DATA SCIENTIST</t>
+          <t>Data Engineer I IS - Remote</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Dollar General</t>
+          <t>Providence</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Goodlettsville, TN, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Data Scientist, Git, Databricks, PySpark, Tableau, Matplotlib, Python, SQL, R, Scala</t>
+          <t>RAG, CI/CD, Git, Snowflake, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93f3bbe6c6eb3335</t>
+          <t>https://www.indeed.com/viewjob?jk=515521aba1ae230b</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Junior Software Engineer</t>
+          <t>Data Engineer I IS - Remote</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>HouseMax Funding</t>
+          <t>Providence</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Git, PostgreSQL, Python, SQL, R, Java, Scala</t>
+          <t>RAG, CI/CD, Git, Snowflake, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43db0fee933b6487</t>
+          <t>https://www.indeed.com/viewjob?jk=8c7e81a454d87de6</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>AI Platform Engineer</t>
+          <t>Data Engineer I IS - Remote</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Abbott</t>
+          <t>Providence</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Napa, CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Generative AI, MLflow, Kubernetes, CI/CD, Git, Python, R, Java, Optimization</t>
+          <t>RAG, CI/CD, Git, Snowflake, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd7f92ef422e6865</t>
+          <t>https://www.indeed.com/viewjob?jk=5418125ceb426870</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Digital Technology Organization Rotational Engineer</t>
+          <t>Data Engineer I IS - Remote</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>PENNYMAC</t>
+          <t>Providence</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Carrollton, TX, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RAG, Gemini, Copilot, Prompt Engineering, Git, MySQL, Python, SQL, R</t>
+          <t>RAG, CI/CD, Git, Snowflake, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ece014134dbfb6ce</t>
+          <t>https://www.indeed.com/viewjob?jk=aec5b5a950be462e</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Data Engineer I IS - Remote</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Super Micro Computer, Inc.</t>
+          <t>Providence</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Redmond, WA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Docker, Git, Hadoop, NoSQL, Python, SQL, R</t>
+          <t>RAG, CI/CD, Git, Snowflake, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5e68423d25b95a9</t>
+          <t>https://www.indeed.com/viewjob?jk=f848c786b8b1acde</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Database Engineer - Remote</t>
+          <t>Data Engineer I IS - Remote</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Providence</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Lubbock, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>CI/CD, Git, PostgreSQL, MySQL, Python, SQL, R, Scala, Optimization</t>
+          <t>RAG, CI/CD, Git, Snowflake, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=341b8b7d68e7994b</t>
+          <t>https://www.indeed.com/viewjob?jk=651a244fe25737e3</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Engineering</t>
+          <t>Software Engineer II (Java/Agentic)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, Terraform, Git, Kafka, SQL, R, Java, Scala</t>
+          <t>RAG, Docker, CI/CD, Terraform, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b1070c522d395ed</t>
+          <t>https://www.indeed.com/viewjob?jk=1dcdf019792c8117</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Cyber Threat Defense Sr AI/ML Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Bank of America</t>
+          <t>Rooms To Go</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Seffner, FL, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Generative AI, LangChain, RAG, Hugging Face, PyTorch, Python, R, Scala</t>
+          <t>Copilot, Docker, GitHub Actions, Git, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5aecf5dad5b36ed</t>
+          <t>https://www.indeed.com/viewjob?jk=4e178d76a96a2a84</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Agentic AI Engineer</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Evergen</t>
+          <t>Instacart</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, Copilot, Git, Snowflake, Python, R, Scala</t>
+          <t>RAG, Copilot, Snowflake, Tableau, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,217 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e547dd05c4bd930</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Senior Developer – Full Stack</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>NuAxis Innovations</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Washington, DC, US USA</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
-        <v>10</v>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, Kubernetes, CI/CD, Kafka, MySQL, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9606ad9dcbf80460</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>IT Web Developer</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>NuAxis Innovations</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Washington, DC, US USA</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>10</v>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>Copilot, S3, CI/CD, Git, Kafka, PostgreSQL, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4300e851986e6585</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Data Scientist</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>HDR</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Sioux Falls, SD, US USA</t>
-        </is>
-      </c>
-      <c r="D40" t="n">
-        <v>10</v>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Tableau, Power BI, Matplotlib, Seaborn, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a639c248a691afa1</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Economist, Ramp Economics Lab</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Ramp</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
-        <v>10</v>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Redshift, BigQuery, Snowflake, BigQuery, Redshift, SQL, R</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c533c1cf2527666a</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Economist, Ramp Economics Lab</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Ramp</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D42" t="n">
-        <v>10</v>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Redshift, BigQuery, Snowflake, BigQuery, Redshift, SQL, R</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e749d6169f5f9a7c</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Senior Data Analyst</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Instacart</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D43" t="n">
-        <v>10</v>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, Snowflake, Tableau, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=111187c8fe573b22</t>
+          <t>https://www.indeed.com/viewjob?jk=fa56d78d0169a083</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-09-01.xlsx
+++ b/daily_matches/job_matches_2026-09-01.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,82 +468,82 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Security Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Aramark</t>
+          <t>DoorDash</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>22.2</v>
+        <v>20</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Copilot, S3, EC2, BigQuery, FastAPI, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform</t>
+          <t>RAG, Redshift, BigQuery, Kinesis, Dataflow, Docker, Kubernetes, CI/CD, Git, Snowflake</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39460deda6cc7046</t>
+          <t>https://www.indeed.com/viewjob?jk=b31c422fadc318ca</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II, Document &amp; Vision Intelligence</t>
+          <t>Consulting SWE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>LexisNexis Risk Solutions</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>22.2</v>
+        <v>18.9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, RAG, TensorFlow, PyTorch, Keras, Docker, Kubernetes</t>
+          <t>RAG, Copilot, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Git, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43f2ff091a75531a</t>
+          <t>https://www.indeed.com/viewjob?jk=0b372b96d1263fff</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II, Document &amp; Vision Intelligence</t>
+          <t>Data Engineer, Data and Insights</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>United Jewish Appeal-Fed of Jewish</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -552,33 +552,33 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>22.2</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, RAG, TensorFlow, PyTorch, Keras, Docker, Kubernetes</t>
+          <t>Data Scientist, RAG, Data Lake, Docker, Kubernetes, CI/CD, Terraform, Git, PySpark, PostgreSQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1dde48c17b527b0d</t>
+          <t>https://www.indeed.com/viewjob?jk=1faa4e13a3b0f326</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II, Document &amp; Vision Intelligence</t>
+          <t>Senior Software Engineer - PA053</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>ZoomInfo</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -587,46 +587,46 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>22.2</v>
+        <v>15.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, RAG, TensorFlow, PyTorch, Keras, Docker, Kubernetes</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, Kafka, MongoDB, NoSQL, SQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=341131fbbffbdd46</t>
+          <t>https://www.indeed.com/viewjob?jk=571921f25acb7de3</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Solutions Architect</t>
+          <t>Senior Software Engineer - PA051</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Smart Tech Skills LLC</t>
+          <t>ZoomInfo</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>15.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>S3, Glue, Synapse, CI/CD, Terraform, Git, Snowflake, Databricks, PySpark, Kafka</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, Kafka, MongoDB, NoSQL, SQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=501460a7402af538</t>
+          <t>https://www.indeed.com/viewjob?jk=c9cfb23165ea9cf6</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Senior AI Engineer (Ph.D. required)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Pacific Gas and Electric</t>
+          <t>Exponent</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Redshift, Synapse, Data Lake, CI/CD, Terraform, Redshift, NoSQL</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Copilot, Pinecone, Prompt Engineering, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c7c0ea011bc1581</t>
+          <t>https://www.indeed.com/viewjob?jk=319bc8e5b3095ebf</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Campus Graduate Masters Summer Internship Program - 2027 Data Engineer, Enterprise Technology Services- Charlotte, NC</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>REPAY</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, CI/CD, Git, BigQuery, PostgreSQL, MongoDB, Cassandra, NoSQL, Python</t>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, Prompt Engineering, AWS SageMaker, CI/CD, Databricks, Python, SQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=615c775c5cae3f87</t>
+          <t>https://www.indeed.com/viewjob?jk=ab319af896ef3105</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Campus Graduate Masters Summer Internship Program - 2027 Data Engineer, Enterprise Technology Services- Phoenix, AZ</t>
+          <t>Senior Backend Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Re:Build Manufacturing</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, CI/CD, Git, BigQuery, PostgreSQL, MongoDB, Cassandra, NoSQL, Python</t>
+          <t>LangChain, RAG, Copilot, FastAPI, Docker, CI/CD, Terraform, PostgreSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7c88978b19e1fac</t>
+          <t>https://www.indeed.com/viewjob?jk=f5186c2e57a8da80</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Campus Graduate Masters Summer Internship Program - 2027 Data Engineer, Enterprise Technology Services- Sunrise, FL</t>
+          <t>Senior Backend Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Re:Build Manufacturing</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, CI/CD, Git, BigQuery, PostgreSQL, MongoDB, Cassandra, NoSQL, Python</t>
+          <t>LangChain, RAG, Copilot, FastAPI, Docker, CI/CD, Terraform, PostgreSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24d421e34cea4cb0</t>
+          <t>https://www.indeed.com/viewjob?jk=d4f9f0680e6340ce</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Business Analyst</t>
+          <t>Senior SecDevOps Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Ness Digital Engineering</t>
+          <t>Re:Build Manufacturing</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Redshift, BigQuery, Kinesis, Git, Snowflake, Databricks, BigQuery, Redshift, Kafka, NoSQL</t>
+          <t>Copilot, Docker, CI/CD, GitHub Actions, Terraform, Git, PostgreSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef3f1d7e3dce5d5b</t>
+          <t>https://www.indeed.com/viewjob?jk=49b77b548d132ade</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Business Analyst</t>
+          <t>Senior Backend Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Ness Digital Engineering</t>
+          <t>Re:Build Manufacturing</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Redshift, BigQuery, Kinesis, Git, Snowflake, Databricks, BigQuery, Redshift, Kafka, NoSQL</t>
+          <t>LangChain, RAG, Copilot, FastAPI, Docker, CI/CD, Terraform, PostgreSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,59 +846,59 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26924b3ed57d2d37</t>
+          <t>https://www.indeed.com/viewjob?jk=1da450a8030e1556</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior AI Engineer (Ph.D. required)</t>
+          <t>Senior SecDevOps Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Exponent</t>
+          <t>Re:Build Manufacturing</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Copilot, Pinecone, Prompt Engineering, Docker, Kubernetes</t>
+          <t>Copilot, Docker, CI/CD, GitHub Actions, Terraform, Git, PostgreSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89ff4cd5ab679967</t>
+          <t>https://www.indeed.com/viewjob?jk=fa41aecb1be7e339</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Campus Undergraduate Summer Internship Program - 2027 Data Engineer, Enterprise Technology Services- Phoenix, AZ</t>
+          <t>Senior SecDevOps Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Re:Build Manufacturing</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Git, BigQuery, PostgreSQL, MongoDB, Cassandra, Python, SQL, R</t>
+          <t>Copilot, Docker, CI/CD, GitHub Actions, Terraform, Git, PostgreSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21c4624adc67b18e</t>
+          <t>https://www.indeed.com/viewjob?jk=f6cff7b7ecdf07ee</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Campus Undergraduate Summer Internship Program - 2027 Data Engineer, Enterprise Technology Services- Charlotte, NC</t>
+          <t>Senior Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Komodo Health</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Git, BigQuery, PostgreSQL, MongoDB, Cassandra, Python, SQL, R</t>
+          <t>RAG, Gemini, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Databricks, Python, R</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a1f26919bbd5f4b</t>
+          <t>https://www.indeed.com/viewjob?jk=8d8d0e684df7d418</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Campus Undergraduate Summer Internship Program - 2027 Data Engineer, Enterprise Technology Services- Sunrise, FL</t>
+          <t>Senior Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Komodo Health</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Git, BigQuery, PostgreSQL, MongoDB, Cassandra, Python, SQL, R</t>
+          <t>RAG, Gemini, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Databricks, Python, R</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,159 +986,159 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f6abea4f1a0a28b</t>
+          <t>https://www.indeed.com/viewjob?jk=5bf57e21b4416003</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Mid-Level DATA ENGINEER: Microsoft Power Platform &amp; AI Copilot Studio (HYBRID)</t>
+          <t>Senior Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>State Farm</t>
+          <t>Komodo Health</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Bloomington, IL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, Synapse, CI/CD, Snowflake, Databricks, Power BI, Python, SQL</t>
+          <t>RAG, Gemini, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Databricks, Python, R</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d276a1bbc3a5d721</t>
+          <t>https://www.indeed.com/viewjob?jk=3faed2f603070d52</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer- REMOTE - Onsite Training</t>
+          <t>Senior Platform Engineer, Product Facing Systems (Remote)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Abercrombie &amp; Fitch</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, NoSQL, Python, SQL</t>
+          <t>RAG, Kubernetes, AKS, CI/CD, Terraform, Git, Kafka, R, Java, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbb47baecd105cce</t>
+          <t>https://www.indeed.com/viewjob?jk=39d31bcfb4ff7ab1</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Software Engineer II (React/Java)</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Kubernetes, CI/CD, Git, Kafka, Cassandra, NoSQL, SQL, R</t>
+          <t>AI Engineer, RAG, CI/CD, Git, Snowflake, Kafka, Hadoop, Python, SQL, R</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68a43b6923d695d9</t>
+          <t>https://www.indeed.com/viewjob?jk=ba3476bddd99dde5</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sr Applied Data Scientist - Personalization (applied ML, PyTorch, RecSys)</t>
+          <t>Junior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>Cortrucent Technologies</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Brooklyn Park, MN, US USA</t>
+          <t>Berlin, NJ, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, PyTorch, Git, Python, SQL, R, Scala</t>
+          <t>RAG, CI/CD, Git, PostgreSQL, MySQL, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bd7f263656a978a</t>
+          <t>https://www.indeed.com/viewjob?jk=c993887da2ecd5ce</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Senior Software Architect, Browser Extension Platform</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CENSYS</t>
+          <t>Keeper Security, Inc.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1147,11 +1147,11 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, Synapse, Docker, Kubernetes, CI/CD, Kafka, Python, R</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, Databricks, R, Java, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37c6fcd4a82da612</t>
+          <t>https://www.indeed.com/viewjob?jk=ee2a9223c60a8a70</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Full Stack Senior Software Developer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Propio LS LLC</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Hugging Face, CI/CD, Python, R, Scala, Optimization</t>
+          <t>Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R, Java, Optimization</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ca8aa6e56948dee</t>
+          <t>https://www.indeed.com/viewjob?jk=828834a8a4fcbd30</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, Accelerated Apache Spark</t>
+          <t>Platform Architect</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>Hyland</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, TensorFlow, PyTorch, XGBoost, Python, SQL, R, Java, Scala, Optimization</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, R, Optimization</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38648a895bf31cd4</t>
+          <t>https://www.indeed.com/viewjob?jk=3af3ecc85ecb69c2</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - WGU Labs</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Western Governors University</t>
+          <t>OrthoFi</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RAG, FastAPI, Docker, Kubernetes, Terraform, PostgreSQL, Python, SQL, R, Scala</t>
+          <t>RAG, Copilot, CI/CD, Terraform, Git, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46d267432b1efe9f</t>
+          <t>https://www.indeed.com/viewjob?jk=1e270a1e6bbcbc5f</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Associate - Full-Stack AI Engineer</t>
+          <t>Data Science Intern - Summer 2027</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>Post Consumer Brands</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Lakeville, MN, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Prompt Engineering, Kubernetes, CI/CD, Python, R, Scala, Optimization</t>
+          <t>Cortex, Snowflake, Databricks, Hadoop, Tableau, Power BI, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54ae268af26a65ff</t>
+          <t>https://www.indeed.com/viewjob?jk=5f257731f67d71f9</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Engineer, Facilities Automation</t>
+          <t>Data Scientist II</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Micron Technology</t>
+          <t>Lennox International</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,42 +1326,42 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Git, Snowflake, Power BI, Python, SQL, R, Scala, Optimization</t>
+          <t>Data Scientist, RAG, TensorFlow, PySpark, Tableau, Power BI, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2bf393f6b205724</t>
+          <t>https://www.indeed.com/viewjob?jk=2a4a075d78546e5e</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Sr. Data Analyst</t>
+          <t>Senior AI Architect</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Reserv</t>
+          <t>SIA</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Git, Snowflake, BigQuery, Tableau, Power BI, Python, SQL, R</t>
+          <t>Generative AI, RAG, Terraform, Git, Databricks, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92c3d91ad7bed240</t>
+          <t>https://www.indeed.com/viewjob?jk=8e029f993870ab2e</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Digital Experience IS Intern: Summer 2027</t>
+          <t>Senior AI Architect</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Blue Cross Blue Shield of Nebraska</t>
+          <t>SIA</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Prompt Engineering, AKS, Git, Python, SQL, R, Java</t>
+          <t>Generative AI, RAG, Terraform, Git, Databricks, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cbdb34dd3cfbe01</t>
+          <t>https://www.indeed.com/viewjob?jk=c5faab720a7e2806</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer I IS - Remote</t>
+          <t>Cloud &amp; AI/AL Architect</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Providence</t>
+          <t>Flash Inspector</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Git, Snowflake, Python, SQL, R, Scala, Optimization</t>
+          <t>AI Engineer, RAG, CI/CD, Git, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=515521aba1ae230b</t>
+          <t>https://www.indeed.com/viewjob?jk=880c4f664a765490</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Engineer I IS - Remote</t>
+          <t>Industrial Engineer -AI Process Entry Level</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Providence</t>
+          <t>Forrest T Jones &amp; Company</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Git, Snowflake, Python, SQL, R, Scala, Optimization</t>
+          <t>Generative AI, RAG, Copilot, Prompt Engineering, Git, Power BI, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c7e81a454d87de6</t>
+          <t>https://www.indeed.com/viewjob?jk=0bc447d63b363416</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Engineer I IS - Remote</t>
+          <t>Junior Software Engineer (Remote)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Providence</t>
+          <t>PolicyMe</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Napa, CA, US USA</t>
+          <t>Ontario, CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Git, Snowflake, Python, SQL, R, Scala, Optimization</t>
+          <t>LangChain, RAG, Prompt Engineering, Git, PostgreSQL, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5418125ceb426870</t>
+          <t>https://www.indeed.com/viewjob?jk=b151b6a784f80621</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineer I IS - Remote</t>
+          <t>Software Engineering PMTS, Enterprise PKI</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Providence</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Git, Snowflake, Python, SQL, R, Scala, Optimization</t>
+          <t>Copilot, Prompt Engineering, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aec5b5a950be462e</t>
+          <t>https://www.indeed.com/viewjob?jk=7d39daec57df4b75</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer I IS - Remote</t>
+          <t>Sr Engineer Site Reliability</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Providence</t>
+          <t>Optimum</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Redmond, WA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Git, Snowflake, Python, SQL, R, Scala, Optimization</t>
+          <t>RAG, Kubernetes, CI/CD, Terraform, Git, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f848c786b8b1acde</t>
+          <t>https://www.indeed.com/viewjob?jk=c89d28ac87de40ac</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer I IS - Remote</t>
+          <t>Data Scientist II</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Providence</t>
+          <t>CareSource</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Lubbock, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Git, Snowflake, Python, SQL, R, Scala, Optimization</t>
+          <t>Data Scientist, Snowflake, Databricks, Power BI, Python, SQL, R, Optimization, A/B Testing</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=651a244fe25737e3</t>
+          <t>https://www.indeed.com/viewjob?jk=5e27a31011904372</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Software Engineer II (Java/Agentic)</t>
+          <t>Data Scientist III</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>CareSource</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,87 +1641,17 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RAG, Docker, CI/CD, Terraform, Git, Python, R, Java, Scala</t>
+          <t>Data Scientist, Snowflake, Databricks, Power BI, Python, SQL, R, Optimization, A/B Testing</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1dcdf019792c8117</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Sr. Software Engineer</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Rooms To Go</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Seffner, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>10</v>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>Copilot, Docker, GitHub Actions, Git, SQL, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4e178d76a96a2a84</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Senior Data Analyst</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Instacart</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>CA, US USA</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>10</v>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, Snowflake, Tableau, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fa56d78d0169a083</t>
+          <t>https://www.indeed.com/viewjob?jk=3c7c100b115bb56e</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-09-01.xlsx
+++ b/daily_matches/job_matches_2026-09-01.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:G53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Security Data Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>DoorDash</t>
+          <t>DailyPay Inc</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20</v>
+        <v>24.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, Redshift, BigQuery, Kinesis, Dataflow, Docker, Kubernetes, CI/CD, Git, Snowflake</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, Azure ML, S3, EC2, Glue, Docker</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b31c422fadc318ca</t>
+          <t>https://www.indeed.com/viewjob?jk=059d00b010e64ab8</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Consulting SWE</t>
+          <t>GCP Architect</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>LexisNexis Risk Solutions</t>
+          <t>J2B GLOBAL LLC</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Columbus, IN, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.9</v>
+        <v>17.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Git, Kafka, PostgreSQL</t>
+          <t>Generative AI, RAG, BigQuery, Dataflow, MLflow, Docker, Kubernetes, CI/CD, Snowflake, Databricks</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,67 +531,67 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b372b96d1263fff</t>
+          <t>https://www.indeed.com/viewjob?jk=794b8cc5a876cb0f</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer, Data and Insights</t>
+          <t>Senior Engineer - Circlecard</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>United Jewish Appeal-Fed of Jewish</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Brooklyn Park, MN, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16.7</v>
+        <v>17.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Data Lake, Docker, Kubernetes, CI/CD, Terraform, Git, PySpark, PostgreSQL</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1faa4e13a3b0f326</t>
+          <t>https://www.indeed.com/viewjob?jk=9dcd68ea69d63903</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - PA053</t>
+          <t>Backend Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ZoomInfo</t>
+          <t>Fellow</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15.6</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, Kafka, MongoDB, NoSQL, SQL</t>
+          <t>LangChain, RAG, S3, Docker, CI/CD, Jenkins, GitHub Actions, Terraform, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=571921f25acb7de3</t>
+          <t>https://www.indeed.com/viewjob?jk=3c077d0d8d52c113</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - PA051</t>
+          <t>Software Engineer, Identity and Access Management</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ZoomInfo</t>
+          <t>Fitch Group</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15.6</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, Kafka, MongoDB, NoSQL, SQL</t>
+          <t>LangChain, RAG, LLaMA, Copilot, Prompt Engineering, Kubernetes, CI/CD, GitHub Actions, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,102 +636,102 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9cfb23165ea9cf6</t>
+          <t>https://www.indeed.com/viewjob?jk=4316a6d89bd9dfac</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior AI Engineer (Ph.D. required)</t>
+          <t>Senior Engineer – Apply For CircleCard</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Exponent</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Brooklyn Park, MN, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.4</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Copilot, Pinecone, Prompt Engineering, Docker, Kubernetes</t>
+          <t>AI Engineer, LangChain, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Kafka, PostgreSQL, Python</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=319bc8e5b3095ebf</t>
+          <t>https://www.indeed.com/viewjob?jk=9dc57cd1efbc6ee0</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>REPAY</t>
+          <t>UCLA Health</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14.4</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, Prompt Engineering, AWS SageMaker, CI/CD, Databricks, Python, SQL</t>
+          <t>RAG, AWS SageMaker, S3, BigQuery, Synapse, MLflow, CI/CD, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab319af896ef3105</t>
+          <t>https://www.indeed.com/viewjob?jk=2834f9c283bafcc9</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer</t>
+          <t>Senior Platform &amp; SRE Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Re:Build Manufacturing</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.3</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Copilot, FastAPI, Docker, CI/CD, Terraform, PostgreSQL, Python, SQL</t>
+          <t>Generative AI, RAG, Gemini, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5186c2e57a8da80</t>
+          <t>https://www.indeed.com/viewjob?jk=8020034c387753ba</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer</t>
+          <t>Software Engineer III (Full Stack Engineer)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Re:Build Manufacturing</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Copilot, FastAPI, Docker, CI/CD, Terraform, PostgreSQL, Python, SQL</t>
+          <t>RAG, S3, EC2, CI/CD, Git, Kafka, PostgreSQL, Cassandra, Python, SQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4f9f0680e6340ce</t>
+          <t>https://www.indeed.com/viewjob?jk=c984a40e303625f4</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior SecDevOps Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Re:Build Manufacturing</t>
+          <t>MRCOOL, LLC</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Hickory, KY, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Copilot, Docker, CI/CD, GitHub Actions, Terraform, Git, PostgreSQL, Python, SQL, R</t>
+          <t>Generative AI, RAG, Gemini, BigQuery, Data Lake, Dataflow, Apache Airflow, BigQuery, Tableau, Power BI</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49b77b548d132ade</t>
+          <t>https://www.indeed.com/viewjob?jk=4b45327f8bc50c30</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer</t>
+          <t>Automation Engineer with AI</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Re:Build Manufacturing</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Copilot, FastAPI, Docker, CI/CD, Terraform, PostgreSQL, Python, SQL</t>
+          <t>Generative AI, RAG, Gemini, Prompt Engineering, Glue, Docker, CI/CD, Jenkins, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1da450a8030e1556</t>
+          <t>https://www.indeed.com/viewjob?jk=d17e38847f210d44</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior SecDevOps Engineer</t>
+          <t>AI Engineer (contract)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Re:Build Manufacturing</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Copilot, Docker, CI/CD, GitHub Actions, Terraform, Git, PostgreSQL, Python, SQL, R</t>
+          <t>AI Engineer, Generative AI, LangChain, Copilot, CI/CD, Git, MongoDB, Python, SQL, R</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa41aecb1be7e339</t>
+          <t>https://www.indeed.com/viewjob?jk=ab1e83e8eb2debbd</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior SecDevOps Engineer</t>
+          <t>Senior Agentic AI Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Re:Build Manufacturing</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Copilot, Docker, CI/CD, GitHub Actions, Terraform, Git, PostgreSQL, Python, SQL, R</t>
+          <t>AI Engineer, Data Scientist, LangChain, RAG, LLaMA, Prompt Engineering, FastAPI, Python, R, Java</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6cff7b7ecdf07ee</t>
+          <t>https://www.indeed.com/viewjob?jk=43a112aa6c71b862</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Engineer</t>
+          <t>Software Development Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Komodo Health</t>
+          <t>Vantor</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Westminster, CO, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, Gemini, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Databricks, Python, R</t>
+          <t>RAG, FastAPI, Docker, Kubernetes, CI/CD, Terraform, PostgreSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d8d0e684df7d418</t>
+          <t>https://www.indeed.com/viewjob?jk=8e710f46abbef3cf</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Engineer</t>
+          <t>APPLICATION DEVELOPER</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Komodo Health</t>
+          <t>Atos</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Aurora, IL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, Gemini, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Databricks, Python, R</t>
+          <t>RAG, CI/CD, Jenkins, Git, Kafka, PostgreSQL, MongoDB, NoSQL, SQL, R</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bf57e21b4416003</t>
+          <t>https://www.indeed.com/viewjob?jk=b369fd4e854f07bb</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Engineer</t>
+          <t>Principle SRE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Komodo Health</t>
+          <t>Merative</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, Gemini, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Databricks, Python, R</t>
+          <t>RAG, Kubernetes, AKS, CI/CD, Terraform, Kafka, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3faed2f603070d52</t>
+          <t>https://www.indeed.com/viewjob?jk=e4c859aac5cb3cfd</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer, Product Facing Systems (Remote)</t>
+          <t>Junior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Abercrombie &amp; Fitch</t>
+          <t>MyFunded Futures</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, AKS, CI/CD, Terraform, Git, Kafka, R, Java, Scala</t>
+          <t>Machine Learning Engineer, XGBoost, LightGBM, Docker, CI/CD, Snowflake, Databricks, PySpark, Python, SQL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39d31bcfb4ff7ab1</t>
+          <t>https://www.indeed.com/viewjob?jk=457121afc1405134</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>Buyers Edge Platform</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, CI/CD, Git, Snowflake, Kafka, Hadoop, Python, SQL, R</t>
+          <t>RAG, Redshift, Git, Snowflake, Databricks, Redshift, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba3476bddd99dde5</t>
+          <t>https://www.indeed.com/viewjob?jk=1bb53d18980f0f7f</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Junior Full Stack Engineer</t>
+          <t>Software Engineer III - AWS Data Platform Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Cortrucent Technologies</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Berlin, NJ, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Git, PostgreSQL, MySQL, Python, SQL, R, Java, Scala</t>
+          <t>RAG, Glue, Athena, Redshift, CI/CD, Terraform, Redshift, Python, R, Java</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c993887da2ecd5ce</t>
+          <t>https://www.indeed.com/viewjob?jk=f3ab76acf6d9b615</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Software Architect, Browser Extension Platform</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Keeper Security, Inc.</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, Databricks, R, Java, Scala</t>
+          <t>Data Scientist, RAG, Data Lake, Kubernetes, CI/CD, Databricks, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee2a9223c60a8a70</t>
+          <t>https://www.indeed.com/viewjob?jk=5c63b933c1725f3d</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Full Stack Senior Software Developer</t>
+          <t>Sr Data Architect - AI Controls, Governance &amp; Capabilities</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Bank of America</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R, Java, Optimization</t>
+          <t>AI Engineer, Data Scientist, RAG, Synapse, Data Lake, Snowflake, Databricks, Python, SQL, R</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=828834a8a4fcbd30</t>
+          <t>https://www.indeed.com/viewjob?jk=971ffff0ba5763a9</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Platform Architect</t>
+          <t>Databricks Architect</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Hyland</t>
+          <t>Confiz</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, R, Optimization</t>
+          <t>RAG, CI/CD, GitHub Actions, Terraform, Git, Databricks, PySpark, Python, SQL, R</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3af3ecc85ecb69c2</t>
+          <t>https://www.indeed.com/viewjob?jk=b6b5450e0d89b0a1</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AI Security Engineer (GRC)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>OrthoFi</t>
+          <t>SCAN Health Plan</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Lakewood, CA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, Terraform, Git, SQL, R, Java, Scala, Optimization</t>
+          <t>Generative AI, LangChain, RAG, Copilot, Hugging Face, Cortex, Git, Snowflake, SQL, R</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,102 +1266,102 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e270a1e6bbcbc5f</t>
+          <t>https://www.indeed.com/viewjob?jk=5faf3a7bf4d919e1</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Science Intern - Summer 2027</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Post Consumer Brands</t>
+          <t>Unissant</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Lakeville, MN, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Cortex, Snowflake, Databricks, Hadoop, Tableau, Power BI, Python, SQL, R, Scala</t>
+          <t>Data Scientist, RAG, Git, Databricks, Tableau, Power BI, Matplotlib, Seaborn, Python, SQL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f257731f67d71f9</t>
+          <t>https://www.indeed.com/viewjob?jk=be7df02edfb477a0</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Scientist II</t>
+          <t>AI Engineer - Senior</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Lennox International</t>
+          <t>CLOUD5TECH</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PySpark, Tableau, Power BI, Python, SQL, R, Scala</t>
+          <t>AI Engineer, Generative AI, RAG, TensorFlow, PyTorch, Hadoop, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a4a075d78546e5e</t>
+          <t>https://www.indeed.com/viewjob?jk=03f72469f35eb4be</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior AI Architect</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>SIA</t>
+          <t>Infoorigin Inc</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Woodlawn, MD, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Terraform, Git, Databricks, Python, R, Scala, Optimization</t>
+          <t>Data Scientist, spaCy, Apache Airflow, CI/CD, Jenkins, Hadoop, PostgreSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e029f993870ab2e</t>
+          <t>https://www.indeed.com/viewjob?jk=22ffa2ca40c5811c</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior AI Architect</t>
+          <t>Senior Data Scientist – Business Optimization &amp; ML Governance</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>SIA</t>
+          <t>Ally Financial</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Lewisville, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Terraform, Git, Databricks, Python, R, Scala, Optimization</t>
+          <t>Data Scientist, RAG, Git, Snowflake, Python, SQL, R, Scala, Optimization, Hypothesis Testing</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5faab720a7e2806</t>
+          <t>https://www.indeed.com/viewjob?jk=e0a07c6052f97aa2</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Cloud &amp; AI/AL Architect</t>
+          <t>Engineer II (US)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Flash Inspector</t>
+          <t>TD</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Mount Laurel, NJ, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, CI/CD, Git, Python, SQL, R, Scala, Optimization</t>
+          <t>RAG, Docker, Kubernetes, Jenkins, Git, MySQL, NoSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=880c4f664a765490</t>
+          <t>https://www.indeed.com/viewjob?jk=eda3a92f55f143ce</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Industrial Engineer -AI Process Entry Level</t>
+          <t>Azure PostgresSQL DBA</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Forrest T Jones &amp; Company</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, Prompt Engineering, Git, Power BI, SQL, R, Optimization</t>
+          <t>RAG, AKS, CI/CD, GitHub Actions, Terraform, Git, PostgreSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0bc447d63b363416</t>
+          <t>https://www.indeed.com/viewjob?jk=aef1b4b968ae90a4</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Junior Software Engineer (Remote)</t>
+          <t>Azure PostgresSQL DBA</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>PolicyMe</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Ontario, CA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Prompt Engineering, Git, PostgreSQL, Python, SQL, R, Scala</t>
+          <t>RAG, AKS, CI/CD, GitHub Actions, Terraform, Git, PostgreSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b151b6a784f80621</t>
+          <t>https://www.indeed.com/viewjob?jk=a4af507d8fab2b3d</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Software Engineering PMTS, Enterprise PKI</t>
+          <t>Azure PostgresSQL DBA</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Copilot, Prompt Engineering, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+          <t>RAG, AKS, CI/CD, GitHub Actions, Terraform, Git, PostgreSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,54 +1546,54 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d39daec57df4b75</t>
+          <t>https://www.indeed.com/viewjob?jk=4fd041f1258d31dc</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Sr Engineer Site Reliability</t>
+          <t>Azure PostgresSQL DBA</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Optimum</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Terraform, Git, Python, SQL, R, Scala</t>
+          <t>RAG, AKS, CI/CD, GitHub Actions, Terraform, Git, PostgreSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c89d28ac87de40ac</t>
+          <t>https://www.indeed.com/viewjob?jk=b023969136a979a6</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Scientist II</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>CareSource</t>
+          <t>ZoomInfo</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Data Scientist, Snowflake, Databricks, Power BI, Python, SQL, R, Optimization, A/B Testing</t>
+          <t>RAG, Docker, Kubernetes, Kafka, MongoDB, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e27a31011904372</t>
+          <t>https://www.indeed.com/viewjob?jk=90f49b894eaa00d0</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Scientist III</t>
+          <t>Senior Software Development Engineer in Test</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>CareSource</t>
+          <t>Vestmark</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Wakefield, MA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Data Scientist, Snowflake, Databricks, Power BI, Python, SQL, R, Optimization, A/B Testing</t>
+          <t>RAG, Docker, CI/CD, Jenkins, GitHub Actions, Git, Python, SQL, R</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,7 +1651,637 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c7c100b115bb56e</t>
+          <t>https://www.indeed.com/viewjob?jk=a76c7fb5b538af46</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Senior Software Development Engineer in Test</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Vestmark</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>10</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>RAG, Docker, CI/CD, Jenkins, GitHub Actions, Git, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=93a0fd9473921320</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>17587 Software Engineer II - Front End</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Compass Group</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>10</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, CI/CD, Git, Kafka, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6372ec5a33459187</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>17587 Software Engineer II - Front End</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Compass</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>10</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, CI/CD, Git, Kafka, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c3798be3b8500007</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>17587 Software Engineer II- Front End</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Compass</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>10</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, CI/CD, Git, Kafka, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=42bb0be0c4db9cde</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>17587 Software Engineer II - Front End</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Compass Group</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>10</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, CI/CD, Git, Kafka, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2cc6a2816f39a748</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Data Scientist Associate</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>10</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Git, Snowflake, Tableau, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=338a133fe841e9cd</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Solution Architect - Cloud Enablement</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Bronx, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>10</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>RAG, Data Lake, Kubernetes, CI/CD, Git, Power BI, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dbd9147180dfc83d</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence Engineer</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>GRP Solutions</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Texas City, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>10</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, Hadoop, Python, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4cc2f3d8ee29e51b</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Software Engineer - School of Medicine</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Temple University Health System</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Philadelphia, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>10</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>CI/CD, Git, Tableau, Power BI, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bcf1eccccb5733da</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer III</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Peloton</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>10</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, RAG, MySQL, Cassandra, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2b5a249cd1929b0f</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Campus Undergraduate Full-Time Engineer - 2027 AI Engineer I, Enterprise Technology Services- Atlanta, GA</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>American Express</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>10</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, Prompt Engineering, CI/CD, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ba56bbbb77f64c00</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Campus Undergraduate Full-Time Engineer - 2027 AI Engineer I, Enterprise Technology Services- Palo Alto, CA</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>American Express</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>10</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, Prompt Engineering, CI/CD, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f152661adc67bb35</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Campus Graduate Masters Full-Time Engineer - 2027 AI Engineer I, Enterprise Technology Services- Palo Alto, CA</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>American Express</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>10</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, Prompt Engineering, CI/CD, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d66129a38f0e7240</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Campus Graduate Masters Full-Time Engineer - 2027 AI Engineer I, Enterprise Technology Services- Atlanta, GA</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>American Express</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>10</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, Prompt Engineering, CI/CD, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=84d4513fe4e17061</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Campus Graduate Masters Full-Time Engineer - 2027 AI Engineer I, Enterprise Technology Services- Phoenix, AZ</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>American Express</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>10</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, Prompt Engineering, CI/CD, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1b0cdc87374bb0d5</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Campus Undergraduate Full-Time Engineer - 2027 AI Engineer I, Enterprise Technology Services- Phoenix, AZ</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>American Express</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>10</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, Prompt Engineering, CI/CD, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7c1fd84f3daf029d</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Data Scientist II</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>CorVel Corporation</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Irvine, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>10</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, AWS SageMaker, Python, SQL, R, Scala, Optimization, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ed1681e86c5be099</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Systems Engineer</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Perzsi LLC</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>10</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, PostgreSQL, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6ebf93230ed85831</t>
         </is>
       </c>
     </row>
